--- a/grc-workpapers/PwC_Connect_Controls.xlsx
+++ b/grc-workpapers/PwC_Connect_Controls.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$B$2:$H$46</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,77 +19,27 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -100,51 +49,33 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </right>
       <top/>
       <bottom/>
@@ -152,89 +83,45 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="00000000"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -317,44 +204,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -381,32 +268,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -433,24 +302,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -462,162 +313,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -627,134 +482,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="B2:H74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.109375" customWidth="1" min="2" max="2"/>
-    <col width="20.77734375" customWidth="1" min="3" max="3"/>
-    <col width="54.33203125" customWidth="1" min="4" max="4"/>
-    <col width="20.77734375" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24.11" customWidth="1" min="2" max="2"/>
+    <col width="20.78" customWidth="1" min="3" max="3"/>
+    <col width="54.33" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Application</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Control Description</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control  </t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="144" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="5" t="inlineStr">
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Control no.: G18f - Assignment of roles in SAP ECC, granted outside SAP GRC AC, is approved by GRA team
 Assignment of roles in SAP ECC, granted outside SAP GRC AC, is approved by GRA team. All requests for user creations or role provisioning in SAP ECC, which is not handled through SAP GRC AC is processed by the IBM SNC Team. Requests for manual user creation/role provisioning is raised as SNOW tickets. IBM SNC Team ensures that the necessary approvals are taken from GRA team before creating the users or assigning the roles to the requested users. 
 Please provide documentation for April 2026 and May 2026</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>G18f - Assignment of roles in SAP ECC</t>
         </is>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="H3" s="12" t="n"/>
-    </row>
-    <row r="4" ht="144" customHeight="1">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="H3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Control no.: GEN.ITGC.2.1.GRCX - Admin / Super user access rights to GRC application are periodically reviewed for appropriateness (NG5+GP1).: 
 All users with access to SAP GRC AC is reviewed to ensure that access is restricted to users with a work related need for this access. Access Ambassador: GRA team extract log of users having access to SAP GRC AC, all users status are validated against SAP to identify if user is active /inactive. Access for users with inactive status are revoked from GRC AC. GRA staff access is reviewed by GRA AC team manager to ensure access is restricted to authorised users. 
 Please provide sample Q1 2026 and Q2 2026</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>GEN.ITGC.2.1.GRCX - Admin</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-    </row>
-    <row r="5" ht="144" customHeight="1">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Please provide the latest review of SoD rulesets:
 • SAP ECC / FACT
@@ -764,94 +619,89 @@
 • CargoWiseOne vs. SAP S/4 HANA NFTP (NR5)</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SAP ECC / FACT</t>
         </is>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-    </row>
-    <row r="6" ht="144" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Kewill / BluJay TMFF</t>
         </is>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-    </row>
-    <row r="7" ht="144" customHeight="1">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Kewill / BluJay TMFF vs. SAP</t>
         </is>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-    </row>
-    <row r="8" ht="144" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>CargoWiseOne</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="144" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="24" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>CargoWiseOne vs. SAP S/4 HANA NFTP (NR5)</t>
         </is>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="144" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Please provide the following documentation: 
 1. GRC blueprints, governance documents, procedures and guidelines covering modules of GRC: 
@@ -866,24 +716,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="144" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>G18C(I) - Review of SAP- FACT Access of users with department change
 Please provide documentation for for April 2026 and May 2026
@@ -891,33 +740,48 @@
 Please provide documentation for for April 2026 and May 2026</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>G18C(I) - Review of SAP-FACT access of users with department change
-G18c - Periodic review of leavers access (SAP Operational &amp; Non-Operational users)</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>G18C(I) - Review of SAP-FACT access of users with department change</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="H11" s="12" t="n"/>
-    </row>
-    <row r="12" ht="144" customHeight="1">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>G18c - Periodic review of leavers access (SAP Operational &amp; Non-Operational users)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>SoD Conflict Report and newsletter for April, May and June 2026 (please share both newsletter and the actual excel sheets) 
 • SAP business users
@@ -927,34 +791,109 @@
 • CargoWiseOne</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>SoD Conflict Report &amp; newsletter - SAP business users; SAP IT-users; Non-SAP (Kewill/BluJay TMFF); Kewill vs. SAP; CargoWiseOne</t>
-        </is>
-      </c>
-      <c r="F12" s="26" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>SAP business users</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G13" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="H12" s="26" t="n">
+      <c r="H13" s="3" t="n">
         <v>46174</v>
       </c>
     </row>
-    <row r="13" ht="144" customHeight="1">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SAP IT-users</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Non-SAP (Kewill / BluJay TMFF)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Kewill vs. SAP</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>CargoWiseOne</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Please provide the following documentation: 
 1. List with user ID’s which have had assigned a fire fighter user NWBC --&gt; Setup --&gt; Superuser Management --&gt; Firefighters 
@@ -965,24 +904,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="144" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Please provide the following documentation: Monitoring of the use of firefighter - Please provide review for May and June 2026:
 • Archer report extract for control G21D for May and June 2026
@@ -1006,38 +944,99 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>G21D - Firefighter access log review (SAP FACT)
-G27a - FF access requests auto-blocked for approval
-G27b - Active firefighter users reviewed
-G27c - Missing firefighter log reviews monitored
-G27d - FF owners &amp; controllers pre-approved</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>G21D - Firefighter access log review (SAP FACT)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>G27a - FF access requests auto-blocked for approval</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>G27b - Active firefighter users reviewed</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G21" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="H14" s="26" t="n">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="15" ht="144" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>G27c - Missing firefighter log reviews monitored</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>G27d - FF owners &amp; controllers pre-approved</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Downloading the ruleset
 To download the ruleset: 
@@ -1060,24 +1059,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="144" customHeight="1">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Please provide the following documentation:
 1.    List with Role Owners.
@@ -1099,24 +1097,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="144" customHeight="1">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>SAP GRC LnS</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>This request is for the upload of:
 • Extract of all critical roles for LnS
@@ -1124,24 +1121,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="144" customHeight="1">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>SAP ECC LnS</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>This request is for the upload of performed archer control for LnS:
 • GEN.ITG.ACC.003.GRC.SAP - Privileged user access is reviewed as applicable - SAP (ECC/RP1)
@@ -1149,93 +1145,110 @@
 Please provide documentation for performed control for Q1 and Q2 2026.</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITG.ACC.003.GRC.SAP - Privileged user access reviewed - SAP (ECC/RP1)
-G28a - Review of users with privileged access to SAP Production (ECC/BW/MDG)</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.003.GRC.SAP - Privileged user access reviewed - SAP (ECC/RP1)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="144" customHeight="1">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="H27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>G28a - Review of users with privileged access to SAP Production (ECC/BW/MDG)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3. LnS - Interim audit</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>SAP ECC LnS</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Please provide a list with users who have access to bypass S transaction codes in SAP
 We have attached the extract with parameters for your reference
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="144" customHeight="1">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Please provide change log for client settings (Table T000) in the period 01.01.2026 to today.
 Please provide documentation for Archer control GEN.ITGC.2.22.PP3 (SAP GRC PC) Changes in Client Protection Settings - for February and April 2026
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>GEN.ITGC.2.22.PP3 (SAP GRC PC) - Changes in Client Protection Settings</t>
         </is>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F30" s="3" t="n">
         <v>46054</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G30" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="H20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="144" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="H30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Please provide documentation for monthly SoD analysis (both newsletter and actual excel sheet with data) for May and June 2026: 
 • SAP business processes 
@@ -1250,61 +1263,99 @@
 Samples for May and June 2026.</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>GEN.SOD.C.004 - Review of open SOD conflicts in SAP
-GEN.SOD.C.004.NFTP - Review of open SOD conflicts in SAP (NR5)
-GEN.SOD.C.001 - Review of open SOD conflicts in legacy systems</t>
-        </is>
-      </c>
-      <c r="F21" s="26" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>GEN.SOD.C.004 - Review of open SOD conflicts in SAP</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G31" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H21" s="27" t="inlineStr">
-        <is>
-          <t>Jan-Apr 2026 (SoD data)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="144" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Jan-Apr 2026 (data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>GEN.SOD.C.004.NFTP - Review of open SOD conflicts in SAP (NR5)</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Jan-Apr 2026 (data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>GEN.SOD.C.001 - Review of open SOD conflicts in legacy systems</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Jan-Apr 2026 (data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Please provide governance document in regards to RPA users.
 Please provide overview of RPA users in SAP S/4 HANA NFTP (NR5) and their purpose</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="144" customHeight="1">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Please provide control documentation for the below listed Archer controls: 
 GEN.ITGC.2.23.PP3 - Review of users with privileged access to SAP (Including NR5, NS5, NE5, NT5, NM5, NB5, NG5, NF5 &amp; TA5) - Please provide review for Q1 and Q2 2026
@@ -1318,132 +1369,240 @@
 GEN.ITGC.2.30.PP3 - Monitoring of Service User - Please provide review for March and April 2026</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITGC.2.23.PP3 &amp; GEN.ITGC.2.8.PP3 - Review of privileged access to SAP
-GEN.ITGC.2.24.PP3 - Users with standard profiles assigned
-GEN.ITGC.2.25.PP3 - Users with standard role assigned
-GEN.ITGC.2.26.PP3 - Debug with change access monitored
-GEN.ITGC.2.27.PP3 - Direct create/change of roles monitored
-GEN.ITGC.2.28.PP3 - Automatic table change logging monitored
-GEN.ITGC.2.29.PP3 - Direct create/change in User Master monitored
-GEN.ITGC.2.30.PP3 - Monitoring of Service User</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="inlineStr">
-        <is>
-          <t>Q1 &amp; Q2 2026 (2.23, 2.8)</t>
-        </is>
-      </c>
-      <c r="G23" s="26" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.23.PP3 &amp; GEN.ITGC.2.8.PP3 - Review of privileged access to SAP</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.24.PP3 - Users with standard profiles assigned</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="H23" s="26" t="n">
+      <c r="G36" s="3" t="n">
         <v>46113</v>
       </c>
-    </row>
-    <row r="24" ht="144" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.25.PP3 - Users with standard role assigned</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.26.PP3 - Debug with change access monitored</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.27.PP3 - Direct create/change of roles monitored</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.28.PP3 - Automatic table change logging monitored</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.29.PP3 - Direct create/change in User Master monitored</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.30.PP3 - Monitoring of Service User</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Control no.: GEN.ITGC.2.6.PP3  Assignment of roles in SAP NFTP, granted outside SAP GRC AC, is approved by GRA team. 
 Please provide documentation for March 2026 and May 2026</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>GEN.ITGC.2.6.PP3 - Assignment of roles in SAP NFTP granted outside GRC AC</t>
         </is>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F43" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G43" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="H24" s="12" t="n"/>
-    </row>
-    <row r="25" ht="144" customHeight="1">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="H43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>GEN.ITGC.2.1.GRCX - Admin / Super user access rights to GRC application are periodically reviewed for appropriateness (NG5+GRP):
 All users with access to SAP GRC AC is reviewed to ensure that access is restricted to users with a work related need for this access. Access Ambassador: GRA team extract log of users having access to SAP GRC AC, all users status are validated against SAP to identify if user is active /inactive. Access for users with inactive status are revoked from GRC AC. GRA staff access is reviewed by GRA AC team manager to ensure access is restricted to authorised users.  
 Please provide sample Q1 and Q2 2026</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>GEN.ITGC.2.1.GRCX - Admin/Super user access rights to GRC reviewed (NG5+GRP)</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="G25" s="27" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="H25" s="12" t="n"/>
-    </row>
-    <row r="26" ht="144" customHeight="1">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="H44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Please provide the latest review of SoD ruleset, including the distinguishment between LnS, Ocean and TMS business processes</t>
         </is>
       </c>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-    </row>
-    <row r="27" ht="144" customHeight="1">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Please provide the following documentation: 
 1. GRC blueprints, governance documents, procedures and guidelines covering modules of GRC: 
@@ -1460,24 +1619,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-    </row>
-    <row r="28" ht="144" customHeight="1">
-      <c r="A28" s="1" t="n"/>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Please provide the following documentation: 
 1. Downloading the ruleset
@@ -1499,24 +1657,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="144" customHeight="1">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Please provide the following documentation: 
 1. List with user ID’s which have had assigned a fire fighter user
@@ -1528,24 +1685,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="144" customHeight="1">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Please provide the following documentation: 
 • Monitoring of the use of firefighter (GEN.ITGC.2.11.NFTP) - Please provide for May and June 2026
@@ -1575,36 +1731,99 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITGC.2.11.NFTP - Firefighter actions reviewed
-GEN.ITGC.2.10.SAP HANA.GRC - FF access requests auto-blocked
-GEN.ITGC.2.12.PP3 - Active firefighter users &amp; access reviewed
-GEN.ITGC.2.13 - Missing firefighter log reviews monitored
-GEN.ITGC.2.14.SAP HANA.NFTP - FF owners &amp; controllers pre-approved</t>
-        </is>
-      </c>
-      <c r="F30" s="26" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.11.NFTP - Firefighter actions reviewed</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G49" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="144" customHeight="1">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="H49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.10.SAP HANA.GRC - FF access requests auto-blocked</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.12.PP3 - Active firefighter users &amp; access reviewed</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.13 - Missing firefighter log reviews monitored</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.14.SAP HANA.NFTP - FF owners &amp; controllers pre-approved</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Please provide the following documentation: 
 1. List with Role Owners.
@@ -1626,20 +1845,19 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any. </t>
         </is>
       </c>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="144" customHeight="1">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Please share documentation for performed control:
 • GEN.ITG.ACC.002.GRC.SAP HANA.NFTP Mover access rights are reviewed and removed - SAP HANA (NFTP)
@@ -1649,29 +1867,44 @@
 • June 2026</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITG.ACC.002.GRC.SAP HANA.NFTP - Mover access rights reviewed &amp; removed
-GEN.ITG.ACC.002.GRC.SAP HANA.DB - Mover access rights reviewed &amp; removed</t>
-        </is>
-      </c>
-      <c r="F32" s="26" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.002.GRC.SAP HANA.NFTP - Mover access rights reviewed &amp; removed</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G55" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="144" customHeight="1">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="H55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.002.GRC.SAP HANA.DB - Mover access rights reviewed &amp; removed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr"/>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Please share documentation for performed control: 
 • GEN.ITG.ACC.001.GRC.SAP HANA.NFTP - Leaver access rights are reviewed and removed - SAP HANA (NFTP)
@@ -1681,52 +1914,66 @@
 • June 2026</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITG.ACC.001.GRC.SAP HANA.NFTP - Leaver access rights reviewed &amp; removed
-GEN.ITG.ACC.001.GRC.SAP HANA.DB - Leaver access rights reviewed &amp; removed</t>
-        </is>
-      </c>
-      <c r="F33" s="26" t="n">
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.001.GRC.SAP HANA.NFTP - Leaver access rights reviewed &amp; removed</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G57" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="144" customHeight="1">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="H57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.001.GRC.SAP HANA.DB - Leaver access rights reviewed &amp; removed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>SAP NFTP - GRC</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Please provide an overview of in use Fiori apps for Ocean and LnS entities
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-    </row>
-    <row r="35" ht="144" customHeight="1">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>This request is for the upload of:
 Extract of all critical roles for NFTP
@@ -1734,67 +1981,64 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="144" customHeight="1">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>This request is for: 
 Extract of all role assignments made to users in NFTP for the period 01-01-2026 - to today
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="27" t="inlineStr">
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Jan-Jul 2026</t>
         </is>
       </c>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-    </row>
-    <row r="37" ht="144" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>4. NFTP - Interim audit</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Please provide us a list with users who have access to bypass S transaction codes in SAP NFTP (NR5)
 We have attached the extract we usually receive for your reference.</t>
         </is>
       </c>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-    </row>
-    <row r="38" ht="144" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>SAP GRC ML</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Please provide the following documentation: 
 1. Latest overview of Access Ambassadors
@@ -1802,24 +2046,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="144" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>SAP GRC ML</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Please provide the following documentation:
 1. List with user ID’s which have had assigned a fire fighter user
@@ -1830,24 +2073,23 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="144" customHeight="1">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>SAP GRC ML</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Please provide the following documentation: 
 • Monitoring of the use of firefighter - Please provide review for May and June 2026:
@@ -1870,34 +2112,65 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additionally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITGC.2.11.TMS - Firefighter actions reviewed
-GEN.ITGC.2.13 - Missing firefighter log reviews monitored
-GEN.ITGC.2.14.SAP HANA.Inland - FF owners &amp; controllers pre-approved</t>
-        </is>
-      </c>
-      <c r="F40" s="26" t="n">
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.11.TMS - Firefighter actions reviewed</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>46143</v>
       </c>
-      <c r="G40" s="26" t="n">
+      <c r="G65" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="144" customHeight="1">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="H65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.13 - Missing firefighter log reviews monitored</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITGC.2.14.SAP HANA.Inland - FF owners &amp; controllers pre-approved</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>SAP GRC TMS</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Please provide the following documentation:
 1. List with Role Owners.
@@ -1909,117 +2182,129 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="144" customHeight="1">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>SAP TM  - GRC</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Control no.: GEN.ITG.ACC.001.GRC.SAP HANA.Inland
 On a monthly basis, access rights to applications is reviewed by application manager/ IT team to verify whether the leaver access has been removed immediately.
 Please provide sample for March and June 2026</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>GEN.ITG.ACC.001.GRC.SAP HANA.Inland - Monthly leaver access review</t>
         </is>
       </c>
-      <c r="F42" s="26" t="n">
+      <c r="F69" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G69" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H42" s="12" t="n"/>
-    </row>
-    <row r="43" ht="144" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="H69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>SAP TM  - GRC</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Control no.: GEN.ITG.ACC.002.GRC.SAP HANA.Inland
 On a monthly basis, access rights to applications is reviewed by application manager/ IT team to verify whether the leaver access has been removed immediately.
 Please provide sample for March and June 2026</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>GEN.ITG.ACC.002.GRC.SAP HANA.Inland - Monthly access review</t>
         </is>
       </c>
-      <c r="F43" s="26" t="n">
+      <c r="F70" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="G43" s="26" t="n">
+      <c r="G70" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H43" s="12" t="n"/>
-    </row>
-    <row r="44" ht="144" customHeight="1">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>SAP TMS - GRC</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Please provide sample documentation for the below controls related to SAP TMS Hana database (NS5): 
 • GEN.ITG.ACC.001.GRC SAP HANA.INLAND.DB for March and June 2026.
 • GEN.ITG.ACC.002.GRC SAP HANA.INLAND.DB for March and June 2026.</t>
         </is>
       </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>GEN.ITG.ACC.001.GRC SAP HANA.INLAND.DB - Leaver access review
-GEN.ITG.ACC.002.GRC SAP HANA.INLAND.DB - Mover access review</t>
-        </is>
-      </c>
-      <c r="F44" s="26" t="n">
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.001.GRC SAP HANA.INLAND.DB - Leaver access review</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G71" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="H44" s="12" t="n"/>
-    </row>
-    <row r="45" ht="144" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>GEN.ITG.ACC.002.GRC SAP HANA.INLAND.DB - Mover access review</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr"/>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>This request is for the upload of:
 Extract of all critical roles for SAP TM
@@ -2027,45 +2312,68 @@
 NOTE: For each of the above lists, please provide a screenshot showing the date and time of the extract, and record count if possible. Additonally please also provide a screenshot showing the date and time of the extract and the selected filters if any.</t>
         </is>
       </c>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="12" t="n"/>
-      <c r="G45" s="12" t="n"/>
-      <c r="H45" s="12" t="n"/>
-    </row>
-    <row r="46" ht="144" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>5. SAP TMS - Interim audit</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr"/>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Please provide us a list with users who have access to bypass S transaction codes in SAP
 We have attached the extract we usually receive for your reference.</t>
         </is>
       </c>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="12" t="n"/>
-      <c r="H46" s="12" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H46"/>
-  <mergeCells count="3">
+  <mergeCells count="36">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="B49:B53"/>
     <mergeCell ref="D5:D9"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="C35:C42"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="D19:D23"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="C5:C9"/>
-    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="B13:B17"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;"Aptos"&amp;10 &amp;K000000_x000d_# Classification: Internal</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>